--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 09:09</t>
+    <t xml:space="preserve">2026-09-09 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:37</t>
+    <t xml:space="preserve">2026-09-18 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-09-30 15:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2020_magallanes.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:33</t>
+    <t xml:space="preserve">2026-10-05 03:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
